--- a/Output/27072026_Taux_Noemie 4.xlsx
+++ b/Output/27072026_Taux_Noemie 4.xlsx
@@ -726,7 +726,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1768,7 +1767,7 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>Non_noémisable2</t>
+          <t>Non_Noémisable2</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
@@ -1902,17 +1901,17 @@
         <v>6202</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>12</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.9750039301996541</v>
+        <v>0.9980688767299646</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>MAEE PR+MAEE SANTE RETRAITE + MAEE PNR</t>
+          <t>MAEE PR+MAEE SANTE RETRAITE + MAEE PNR + MTE ACTIF</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1925,17 +1924,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>1114038</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>31661</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>4527</v>
-      </c>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
       <c r="D8" s="9" t="n">
-        <v>0.9685383568098791</v>
+        <v>0.9873206575781186</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -1973,17 +1966,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>6682</v>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>538</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>75</v>
-      </c>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="9" t="n">
-        <v>0.9159698423577793</v>
+        <v>0.9163208852005532</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -2004,13 +1991,13 @@
         <v>99797</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>11820</v>
+        <v>0</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>515</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.8899957193307887</v>
+        <v>0.9948660180237658</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
@@ -2079,13 +2066,13 @@
         <v>11379</v>
       </c>
       <c r="B14" s="8" t="n">
-        <v>8853</v>
+        <v>0</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>16342</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.3111226554382895</v>
+        <v>0.4104830273078172</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -2136,7 +2123,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G16" s="11" t="n"/>
@@ -2155,7 +2142,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G17" s="11" t="n"/>
@@ -2163,16 +2150,16 @@
     <row r="18"/>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>2868655</v>
+        <v>2672006</v>
       </c>
       <c r="B19" s="12" t="n">
-        <v>223687</v>
+        <v>181160</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>178619</v>
+        <v>175912</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.8770067879133991</v>
+        <v>0.8821185852592769</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
@@ -2185,13 +2172,13 @@
         <v>1574007</v>
       </c>
       <c r="B20" s="15" t="n">
-        <v>159099</v>
+        <v>158554</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>149464</v>
+        <v>149461</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.8360948065676177</v>
+        <v>0.8363382574698914</v>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
@@ -2201,16 +2188,16 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>1294648</v>
+        <v>1097999</v>
       </c>
       <c r="B21" s="15" t="n">
-        <v>64588</v>
+        <v>22606</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>29155</v>
+        <v>26451</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.9324808357299925</v>
+        <v>0.9572322536999065</v>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
